--- a/Documentos de pruebas/PTP_HECTOR_CONCHA_09042026.xlsx
+++ b/Documentos de pruebas/PTP_HECTOR_CONCHA_09042026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Héctor Fabio\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\automation\screenplay_hec\Documentos de pruebas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB6EF1D-7C53-4703-B4B6-5CCD2AEB5C63}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C185634-BE66-4C64-8103-A831BC695DDF}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{0876C75C-5030-4ACE-B044-6E3EC2DD4BE3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0876C75C-5030-4ACE-B044-6E3EC2DD4BE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Link de repo" sheetId="6" r:id="rId1"/>
@@ -30,21 +30,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>URL</t>
-  </si>
-  <si>
-    <t>https://github.com/archervaz/qvision2.git</t>
-  </si>
-  <si>
-    <t>product search</t>
   </si>
   <si>
     <t>Flujo de login  y logout desarrollado en postman</t>
   </si>
   <si>
     <t>Se valida la respuesta de los endpoints para el ingreso y cierre de sesion con el fin de garantizar su funcionabilidad, ya en el documento Prueba técnica Qvision., es detalla mas la implementacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> desarrolaldo con Screenplay se garantizar su funcionabilidad, ya en el documento Prueba técnica Qvision., es detalla mas la implementacion</t>
+  </si>
+  <si>
+    <t>Flujo de product search,</t>
+  </si>
+  <si>
+    <t>Flujo deuser_creation.feature,</t>
+  </si>
+  <si>
+    <t>https://github.com/archervaz/screenplay_hec.git</t>
+  </si>
+  <si>
+    <t>git@github.com:archervaz/screenplay_hec.git</t>
   </si>
 </sst>
 </file>
@@ -97,7 +106,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,6 +114,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -161,6 +171,116 @@
         <a:xfrm>
           <a:off x="2766060" y="731521"/>
           <a:ext cx="15223524" cy="7627620"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>40005</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDBA3BBE-DE71-4344-A985-6F478FC35A9C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2270760" y="548640"/>
+          <a:ext cx="10058400" cy="5343525"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>32385</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44E7A392-0D77-401D-97AA-07E586BC44C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1767840" y="541020"/>
+          <a:ext cx="10058400" cy="5343525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -469,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E7F0A-8575-48D5-B3EF-115B2977D315}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="35.44140625" bestFit="1" customWidth="1"/>
@@ -480,12 +600,17 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -494,9 +619,10 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" xr:uid="{DC2A51A5-D1AE-463C-BC5C-EA40A22E980B}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{112FB7E8-351A-4939-8D71-C962515F4C29}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -510,10 +636,10 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -524,28 +650,45 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A9179E6-DA63-4214-907C-2FB56E69CD1F}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF5DEEE0-1B91-4018-B6A7-11A569F38969}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
